--- a/Config/GameConfig/Datas/global.xlsx
+++ b/Config/GameConfig/Datas/global.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UnityProject\Framework\Framework\Config\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B76E7B5C-016C-4B9D-BA33-17FE816E8DD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDDE275B-BF3F-44A3-908D-DD441473197F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
   <si>
     <t>int</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -64,6 +64,30 @@
   </si>
   <si>
     <t>PlayerInitExp</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>FriendlyLandYieldCountBuff</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>土地类型友好的产量增益</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>HostileLandYieldCountBuff</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>土地类型不友好的产量增益</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>WaterSpeedUpGrowTime</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>浇水加快生长时间S</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -175,12 +199,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -467,12 +490,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
     <col min="2" max="2" width="30.625" customWidth="1"/>
-    <col min="3" max="3" width="26.625" customWidth="1"/>
+    <col min="3" max="3" width="27.625" customWidth="1"/>
     <col min="4" max="4" width="19.875" customWidth="1"/>
     <col min="5" max="5" width="14.75" customWidth="1"/>
     <col min="6" max="6" width="32.5" customWidth="1"/>
@@ -493,112 +516,142 @@
       <c r="F1" s="1"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5" t="s">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="5">
         <v>1</v>
       </c>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="5">
         <v>0</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
+      <c r="A6" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="7">
+        <v>30</v>
+      </c>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
+      <c r="A7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="7">
+        <v>-30</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
+      <c r="A8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="7">
+        <v>5</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
